--- a/docs/qms/evidence-2026/19_Excel_Registers/EM26-21_Non_Functional_Requirements.xlsx
+++ b/docs/qms/evidence-2026/19_Excel_Registers/EM26-21_Non_Functional_Requirements.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Issued 2026-10-11 for review and approval</t>
+          <t>APPROVED — 2026-10-12 (AR-2026-003)</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -864,10 +864,14 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>To be confirmed</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
+          <t>Alexander Peter</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -882,10 +886,14 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>To be confirmed</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
+          <t>Sheryl Nazareth</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -900,10 +908,14 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>To be confirmed</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr"/>
+          <t>Anita Johan</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -914,44 +926,92 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Change</t>
-        </is>
-      </c>
+          <t>Approval record</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — review and approval confirmed by each role holder on 2026-10-12. Signatures are their typed names (SOP-01 §6).</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Richard Watson Stephen Amudha (Lead Engineer)</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>First issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Anita Johan (Managing Director)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Approved — AR-2026-003</t>
         </is>
       </c>
     </row>

--- a/docs/qms/evidence-2026/19_Excel_Registers/EM26-21_Non_Functional_Requirements.xlsx
+++ b/docs/qms/evidence-2026/19_Excel_Registers/EM26-21_Non_Functional_Requirements.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NFR register'!$A$4:$N$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025 NFRs'!$A$4:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Measurement history'!$A$4:$F$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Measurement history'!$A$4:$G$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Monitoring plan'!$A$4:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="n"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C8" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>APPROVED — 2026-10-12 (AR-2026-003)</t>
+          <t>Rev 1.0 APPROVED 2026-10-12 (AR-2026-003); rev 1.1 issued 2026-10-12 — approval of the revision to be confirmed</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -767,7 +767,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Every recorded measurement, with date and source (golden suite, paper harness, acceptance runs, CI)</t>
+          <t>Every recorded measurement, with date, version and source (golden suite, paper harness, acceptance runs, CI)</t>
         </is>
       </c>
       <c r="C20" s="2" t="n"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -864,14 +864,10 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Alexander Peter</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
+          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -886,14 +882,10 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Sheryl Nazareth</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
+          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -908,14 +900,10 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Anita Johan</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
+          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -936,7 +924,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — review and approval confirmed by each role holder on 2026-10-12. Signatures are their typed names (SOP-01 §6).</t>
+          <t>Rev 1.0: docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — confirmed by each role holder on 2026-10-12. Rev 1.1 is signed here when they confirm it. Signatures are their typed names (SOP-01 §6).</t>
         </is>
       </c>
       <c r="B31" s="2" t="n"/>
@@ -1012,6 +1000,28 @@
       <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Approved — AR-2026-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha (Lead Engineer)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Versions v1.0.0–v1.4.1 added (v1.0.0–v1.3.0 retrospective baselines, REG-08 §2a); version reviews</t>
         </is>
       </c>
     </row>
@@ -3915,15 +3925,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3948,25 +3959,30 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
           <t>NFR</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Status / note</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
@@ -3980,25 +3996,30 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>29/52</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>First run of the new harness</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-123923.json</t>
         </is>
@@ -4012,25 +4033,30 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>27/52</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-124803.json</t>
         </is>
@@ -4044,25 +4070,30 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>44/52</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-130027.json</t>
         </is>
@@ -4076,25 +4107,30 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>47/52</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-130900.json</t>
         </is>
@@ -4108,25 +4144,30 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>48/52</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-131815.json</t>
         </is>
@@ -4140,25 +4181,30 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>48/52</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-134521.json</t>
         </is>
@@ -4172,25 +4218,30 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>48/52</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-184535.json</t>
         </is>
@@ -4204,25 +4255,30 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>47/52</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-185435.json</t>
         </is>
@@ -4236,25 +4292,30 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>43/52</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-195109.json</t>
         </is>
@@ -4268,25 +4329,30 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>0/7</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Smoke subset (7 questions)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-195914.json</t>
         </is>
@@ -4300,25 +4366,30 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>0/7</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Smoke subset (7 questions)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-200328.json</t>
         </is>
@@ -4332,25 +4403,30 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>48/52</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-201050.json</t>
         </is>
@@ -4364,25 +4440,30 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>48/52</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-203340.json</t>
         </is>
@@ -4396,25 +4477,30 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>49/52</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-204248.json</t>
         </is>
@@ -4428,25 +4514,30 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>48/52</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-215246.json</t>
         </is>
@@ -4460,25 +4551,30 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>46/52</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-224713.json</t>
         </is>
@@ -4492,25 +4588,30 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>48/52</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-225633.json</t>
         </is>
@@ -4524,25 +4625,30 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>48/52</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-225644.json</t>
         </is>
@@ -4556,25 +4662,30 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>48/52</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260729-231034.json</t>
         </is>
@@ -4588,25 +4699,30 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>43/52</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Tuning run</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260730-015940.json</t>
         </is>
@@ -4620,25 +4736,30 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>50/52</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Baseline 50/52 — release gate set at ≥ 49</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260730-020659.json</t>
         </is>
@@ -4652,25 +4773,30 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>42/52</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Regression detected: isolation bypass (NC-2026-001)</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260806-142233.json</t>
         </is>
@@ -4684,25 +4810,30 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>49/52</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>After fix 4e27109</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260806-143249.json</t>
         </is>
@@ -4716,25 +4847,30 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
           <t>NFR-P01</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Paper harness E1</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>median 3.31 s; p95 15.17 s (n=30)</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>Meets</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>eval/paper/results/e1_latency.json</t>
         </is>
@@ -4748,25 +4884,30 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
           <t>NFR-P02 / P03</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Paper harness E1</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Retrieval 2.8 % of latency; filter 0.08 ms</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Meets</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>eval/paper/results</t>
         </is>
@@ -4780,25 +4921,30 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
           <t>NFR-P04</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Paper harness E4</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>First audible reply median 636 ms; p95 894 ms (n=10) vs 866 ms single loop</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>Meets</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>eval/paper/results</t>
         </is>
@@ -4812,25 +4958,30 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
           <t>NFR-P07</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Paper harness E7</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Barge-in stop median 2.13 s; success 1.00 (n=8)</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Does not meet</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>eval/paper/results</t>
         </is>
@@ -4844,25 +4995,30 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q01…Q04</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Paper harness E2/E3/E5</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Citation precision 0.979; recall 0.826; fact support 0.815; abstention 0.783</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>eval/paper/results/SUMMARY.json</t>
         </is>
@@ -4876,25 +5032,30 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
           <t>NFR-S01 / S02 / S03</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Paper harness E6/E8</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>0/50 leaks; 0/359 out-of-namespace; injection 10.2 % → 5.1 %</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>Meets / at boundary</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>eval/paper/results</t>
         </is>
@@ -4908,25 +5069,30 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>v1.4.0</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
           <t>NFR-P05 / P06</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>12 spoken turns, 2 personas</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>First reply 0.14–0.49 s on GPU; final STT 70–130 ms</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>Meets</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>commit ff29843</t>
         </is>
@@ -4940,25 +5106,30 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
+          <t>v1.4.0</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
           <t>NFR-R04</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Restore test</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Restore into a throwaway volume: integrity_check ok, 32 tables</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>Meets</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>backup_checksum_20260922.sha256</t>
         </is>
@@ -4972,25 +5143,30 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
+          <t>v1.4.0</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q05</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Golden suite</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>9/52</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Corpus absent (NC-2026-008) — blocked</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>eval/reports/eval_20260922-135322.json</t>
         </is>
@@ -5004,25 +5180,30 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
+          <t>v1.4.1</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q06, S06–S08, M02</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Acceptance suite run 1</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>4 failures (logout, upload type, small talk, export key formats)</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>15_Testing/Execution_Records/run1</t>
         </is>
@@ -5036,25 +5217,30 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
+          <t>v1.4.1</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
           <t>NFR-Q06, S06–S08, M02</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Acceptance suite run 4 (after fixes)</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>11/11 executable cases pass</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>15_Testing/Execution_Records/run4</t>
         </is>
@@ -5068,25 +5254,30 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
+          <t>v1.4.1</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
           <t>NFR-R03</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Container configuration</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Log rotation 50 MB × 5 on all six containers</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>Meets</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>docker inspect</t>
         </is>
@@ -5100,25 +5291,30 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
+          <t>v1.4.1</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
           <t>NFR-M01, S04</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>Backend 50, voice 131 tests, type-check 0 errors; proven red on a broken test</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>Meets</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>GitHub Actions CI</t>
         </is>
@@ -5132,25 +5328,30 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
+          <t>v1.4.1</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
           <t>NFR-S05</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>External login check</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Unauthenticated API → 401 from GitHub's network, every 6 h</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>Meets</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>public-gate-check workflow</t>
         </is>
@@ -5164,32 +5365,37 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
+          <t>v1.4.1</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
           <t>NFR-R01</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Health checks</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Ollama check makes a real embedding; 4 of 6 services checked</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>docker-compose.yml</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F42"/>
+  <autoFilter ref="A4:G42"/>
   <printOptions gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>

--- a/docs/qms/evidence-2026/19_Excel_Registers/EM26-21_Non_Functional_Requirements.xlsx
+++ b/docs/qms/evidence-2026/19_Excel_Registers/EM26-21_Non_Functional_Requirements.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 APPROVED 2026-10-12 (AR-2026-003); rev 1.1 issued 2026-10-12 — approval of the revision to be confirmed</t>
+          <t>APPROVED — rev 1.1 2026-10-12 (AR-2026-004); rev 1.0 2026-10-12 (AR-2026-003)</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -864,10 +864,14 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
+          <t>Alexander Peter</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -882,10 +886,14 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
+          <t>Sheryl Nazareth</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -900,10 +908,14 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr"/>
+          <t>Anita Johan</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -924,7 +936,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0: docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — confirmed by each role holder on 2026-10-12. Rev 1.1 is signed here when they confirm it. Signatures are their typed names (SOP-01 §6).</t>
+          <t>Rev 1.1: docs/qms/records/approvals/2026-10-12_AR-2026-004_register_revision_approval.md; rev 1.0: …/2026-10-12_AR-2026-003_register_approval.md. Review and approval confirmed by each role holder; signatures are their typed names (SOP-01 §6).</t>
         </is>
       </c>
       <c r="B31" s="2" t="n"/>
@@ -1022,6 +1034,28 @@
       <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Versions v1.0.0–v1.4.1 added (v1.0.0–v1.3.0 retrospective baselines, REG-08 §2a); version reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Anita Johan (Managing Director)</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Approved — AR-2026-004</t>
         </is>
       </c>
     </row>
